--- a/output/faculty_requests/FBE - end-2026 sustainability reporting request.xlsx
+++ b/output/faculty_requests/FBE - end-2026 sustainability reporting request.xlsx
@@ -896,7 +896,9 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>Please describe any innovative approaches used within your Faculty/Portfolio to embed sustainability in teaching and learning. This could include examples of subjects, curriculum design, pedagogies, assessment approaches or learning resources. Please provide links or supporting evidence where available.</t>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+Please provide one or two examples from 2026 of innovative approaches your faculty has used to embed sustainability in teaching and learning (e.g. new or redesigned subjects, curriculum design, pedagogies, assessment approaches or learning resources). Include links to subject pages or resources where available.
+A full list of subjects is not required.</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -952,7 +954,8 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>Please describe any pilots or trials undertaken within your Faculty/Portfolio to understand or strengthen students’ sustainability self-efficacy. This could include the approach used, participating cohorts, what was assessed or learned, and any planned next steps.</t>
+          <t>Has your faculty piloted or trialled any approach in 2026 to understand or build students' confidence and capability to act on sustainability (sustainability self-efficacy)? If yes, briefly describe the approach, participating cohort, what was learned and next steps. If not, please respond 'none in 2026' – this is a new indicator and a nil response is useful.
+We are aware of the Sustainability Strengths Compass Living Lab project (CLLAP) and will collect it separately.</t>
         </is>
       </c>
       <c r="G17" s="19" t="inlineStr">
@@ -999,7 +1002,8 @@
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>Please provide examples of sustainability-focused experiential or co-curricular learning offered or supported by your Faculty/Portfolio (e.g. Wattle Fellowship, Melbourne Plus or similar), could include participation where available and a brief description of the learning experience and outcomes.</t>
+          <t>Please list any sustainability-focused experiential or co-curricular learning opportunities your faculty offered or supported in 2026 (e.g. industry or community projects, fieldwork, internships, student challenges), with approximate student participation where known and a one-line description of outcomes.
+We will collect Wattle Fellowship and Melbourne Plus information centrally – please only include these if your faculty ran a specific activity.</t>
         </is>
       </c>
       <c r="G18" s="19" t="inlineStr">
@@ -1046,7 +1050,8 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>Please provide examples or profiles of graduates or alumni from your Faculty who demonstrate how they apply sustainability knowledge, skills or capabilities through their careers, communities or other activities. Where available, include any evidence used by the Faculty to understand graduate outcomes related to sustainability.</t>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 4b(i) and rated it 'Met or exceeded' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+Please nominate up to two alumni from your faculty whose careers or community work demonstrate how they apply sustainability knowledge and skills (name, course and graduating year, a short summary, a link to a profile if available, and whether consent to be featured is likely). If your faculty tracks sustainability-related graduate outcomes in any way, please briefly describe how.</t>
         </is>
       </c>
       <c r="G19" s="19" t="inlineStr">
@@ -1104,7 +1109,9 @@
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>Please provide examples of researchers within your Faculty/Portfolio contributing to University operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support. Briefly describe the operational challenge, researcher contribution and resulting or expected outcome.</t>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+Please provide up to two examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). For each, briefly describe the operational challenge, the researcher's contribution, the University team involved and the result.
+We will collect Campus Living Lab Accelerator Program (CLLAP) projects separately from CI&amp;S – please include other examples only.</t>
         </is>
       </c>
       <c r="G20" s="19" t="inlineStr">
@@ -1159,7 +1166,7 @@
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>Please describe any pathways, mechanisms or processes within your Faculty/Portfolio that enable ongoing collaboration between academic and professional staff on operational sustainability challenges, could include formal programs, governance arrangements, funding mechanisms or coordination channels.</t>
+          <t>Does your faculty have any mechanism that supports ongoing collaboration between academic and professional staff on operational sustainability (e.g. a sustainability committee with mixed membership, seed funding, a coordination role or a regular forum)? If yes, briefly describe it and how often it operates. If not, please say so.</t>
         </is>
       </c>
       <c r="G21" s="19" t="inlineStr">
@@ -1206,7 +1213,7 @@
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>Please provide an assessment of the quality, relevance and continuity of sustainability-related collaborations involving your Faculty/Portfolio, could include evidence of whether collaborations are sustained, useful to operational priorities and producing relevant outcomes.</t>
+          <t>For the collaborations described in TR1(a)–(b), please give a short assessment (a paragraph is sufficient) of their quality, relevance and continuity: are they ongoing, useful to the University's operational priorities, and producing outcomes?</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
@@ -1253,7 +1260,7 @@
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>Please provide any participant feedback or other evidence from your Faculty/Portfolio on the effectiveness and mutual benefit of collaboration mechanisms between researchers and operational teams, could include key findings and any improvements identified.</t>
+          <t>Has your faculty collected any feedback from participants (researchers or operational staff) on how well these collaboration mechanisms work and whether they are mutually beneficial? If yes, summarise key findings and any improvements identified; if not, please say so.</t>
         </is>
       </c>
       <c r="G23" s="19" t="inlineStr">
@@ -1300,7 +1307,9 @@
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>Please provide examples of sustainability-related research impact from your Faculty/Portfolio across policy, industry, community, practice, cultural or institutional pathways. For key examples, briefly describe the research contribution, partner/user and resulting outcome or influence.</t>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+Please provide one or two examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. For each, briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
+We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from MRE – publication counts are not required.</t>
         </is>
       </c>
       <c r="G24" s="19" t="inlineStr">
@@ -1360,7 +1369,9 @@
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>Please provide case studies from your Faculty/Portfolio demonstrating how research has contributed to meaningful sustainability outcomes. Briefly describe the research, stakeholders involved, pathway to impact and evidence of the resulting sustainability outcome.</t>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+Please provide one case study (up to 300 words) of a research project from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. This can be one of the examples from TR2(a), developed in more detail.
+We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.</t>
         </is>
       </c>
       <c r="G25" s="19" t="inlineStr">
@@ -1420,7 +1431,8 @@
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>Please describe how sustainability considerations are integrated into research systems, planning processes, guidance, training, induction or support services within your Faculty/Portfolio, could include examples of any new or improved processes.</t>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+Please describe how sustainability considerations are built into your faculty's research systems or support – e.g. research planning or approval processes, guidance, graduate researcher induction or training, grant development support. Please highlight any new or improved process introduced in 2026.</t>
         </is>
       </c>
       <c r="G26" s="19" t="inlineStr">
@@ -1479,7 +1491,8 @@
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>Please describe any efforts within your Faculty/Portfolio to make research practices more sustainable, could include examples from laboratories, fieldwork, procurement, research travel or infrastructure use. Where available, provide evidence of uptake, resource savings, emissions reductions or other outcomes.</t>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please describe up to two examples and any evidence of uptake, resource savings or emissions reductions.</t>
         </is>
       </c>
       <c r="G27" s="19" t="inlineStr">
@@ -1538,7 +1551,7 @@
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>Please provide evidence of progress in sustainability-related research culture, capability and awareness within your Faculty/Portfolio. This could include relevant staff and/or graduate researcher survey findings, participation in capability-building activities, or other indicators of change over time.</t>
+          <t>Does your faculty have any evidence of change in sustainability-related research culture, capability or awareness – e.g. results from staff or graduate researcher surveys, or participation in capability-building events or training? Please provide a brief summary and the source. If no evidence is available, please say so.</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
@@ -1585,7 +1598,7 @@
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>Faculty/Portfolio’s assessment of progress in embedding sustainable research practices, highlighting areas of strong progress, remaining gaps and priority actions for further improvement.</t>
+          <t>Drawing on your responses to TR3(a)–(c), please provide a short overall assessment (2–3 sentences) of your faculty's progress in embedding sustainable research practices: where progress is strongest, the main gaps, and priority actions for 2027.</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
@@ -1632,7 +1645,8 @@
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>Please list and describe examples of communications from your Faculty/Portfolio that demonstrate climate action, research and learning and aim to inform policy, sector or community decarbonisation efforts. Could include links, intended audiences and any available evidence of reach or influence.</t>
+          <t>Please list up to three examples of 2026 communications from your faculty that showcase climate action, research or learning and aim to inform policy, sector or community decarbonisation (e.g. policy submissions, public events, media, reports). Include links, the intended audience and any reach data you have.
+This will also contribute to the University's mapping of decarbonisation-related research and education (due by 2028).</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
@@ -1679,7 +1693,8 @@
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>List and describe communications from the faculty in terms of climate action, research and learning to inform policy, sector and community decarbonisation efforts</t>
+          <t>If not already covered in CL2(a), please list any ongoing channels or programs (e.g. event series, newsletters, podcasts, policy engagement) through which your faculty regularly communicates climate research and learning to policy, sector or community audiences. You may respond 'see CL2(a)' if already covered.
+We will also engage Melbourne Climate Futures and the Melbourne Energy Institute.</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
@@ -1726,7 +1741,8 @@
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>Please provide examples or case studies from your Faculty/Portfolio of sustainability outcomes informed by Indigenous knowledges. Describe the activity or decision, how Indigenous knowledges were incorporated or co-created, who was involved, and the resulting sustainability outcome.</t>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 6a and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+Please provide one case study of an activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
@@ -1788,7 +1804,9 @@
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>Comment on living labs in the Faculty - outputs, outcomes, and impact</t>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+Please provide a case study of a living lab which operates within your faculty, including a description of its activities, who is involved (students, researchers, operational staff) and its outputs, outcomes or impact in 2026.
+Please note we will approach living labs funded through the Campus Living Lab Accelerator Program (CLLAP) separately.</t>
         </is>
       </c>
       <c r="G33" s="19" t="inlineStr">
@@ -1843,7 +1861,8 @@
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and provide a short description of one that has contributed to a Sustainability 2030 outcome.</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
@@ -1899,7 +1918,7 @@
       </c>
       <c r="F35" s="19" t="inlineStr">
         <is>
-          <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your Faculty/Portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
+          <t>Please describe how sustainability is built into your faculty's governance and decision-making – e.g. a sustainability committee or Associate Dean (Sustainability) role, a faculty sustainability action plan, sustainability criteria in planning or approvals, and how progress is reported (e.g. to the Faculty Executive). Please link the action plan if one exists.</t>
         </is>
       </c>
       <c r="G35" s="19" t="inlineStr">
@@ -2088,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="B1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2112,6 +2131,21 @@
           <t>Y/N</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Target status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Response count</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -2134,6 +2168,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -2156,6 +2201,17 @@
           <t>No</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -2178,6 +2234,17 @@
           <t>TBC</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -2189,6 +2256,17 @@
         <is>
           <t>Support meeting</t>
         </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">

--- a/output/faculty_requests/FBE - end-2026 sustainability reporting request.xlsx
+++ b/output/faculty_requests/FBE - end-2026 sustainability reporting request.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Exceptional education section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will collate examples of innovative sustainability teaching and learning across faculties to inform the Exceptional education section of the 2026 Sustainability Report, and select one or two for short case studies.</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Exceptional education section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
       <c r="H17" s="19" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Exceptional education section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will combine faculty examples with central Wattle Fellowship and Melbourne Plus data to report on the range and reach of sustainability-focused experiential and co-curricular learning across the University.</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Exceptional education section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will use nominated alumni to develop short graduate profiles for the 2026 Sustainability Report (subject to consent), and record any faculty approaches to tracking graduate outcomes to inform how this indicator is measured from 2027.</t>
         </is>
       </c>
       <c r="H19" s="19" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G20" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside CLLAP projects reported by CI&amp;S, and share them with operational teams to identify further collaboration.</t>
         </is>
       </c>
       <c r="H20" s="19" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="G21" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will map existing academic–professional collaboration mechanisms across faculties to establish a baseline for this new indicator and identify models other faculties could adopt.</t>
         </is>
       </c>
       <c r="H21" s="19" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="G22" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will use your assessment to describe the quality and continuity of research–operations collaboration in the 2026 report, and as baseline evidence for the interim target status assessment from 2027.</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="G23" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will use any feedback to understand whether collaboration mechanisms are working and to inform improvements. Where none has been collected, this helps us plan how to gather feedback from 2027.</t>
         </is>
       </c>
       <c r="H23" s="19" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G24" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from MRE.</t>
         </is>
       </c>
       <c r="H24" s="19" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="G25" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
       <c r="H25" s="19" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G26" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on how sustainability is being built into research systems and support across the University, and use responses to establish a baseline for this new target.</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="G27" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
       <c r="H27" s="19" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will use any survey or capability data to describe changes in sustainability-related research culture. Where no evidence exists, this helps us plan University-wide measurement (e.g. staff and graduate researcher surveys) from 2027.</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will use faculty self-assessments to identify strengths, gaps and priority actions in embedding sustainable research practices, to inform internal management reporting and the Transformational research working group.</t>
         </is>
       </c>
       <c r="H29" s="19" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Climate leadership section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will use these examples to show how the University communicates climate research and learning to external audiences, and as an input to the institutional decarbonisation research and education mapping due by 2028.</t>
         </is>
       </c>
       <c r="H30" s="19" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="G31" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Climate leadership section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on the University's ongoing climate communications in the Climate leadership section of the 2026 Sustainability Report, alongside contributions from Melbourne Climate Futures and the Melbourne Energy Institute.</t>
         </is>
       </c>
       <c r="H31" s="19" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Enablers section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
       <c r="H32" s="19" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="G33" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Enablers section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will share examples of living labs from across the University in the 2026 Sustainability Report, alongside CLLAP projects reported by CI&amp;S.</t>
         </is>
       </c>
       <c r="H33" s="19" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Enablers section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
       <c r="H34" s="19" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="G35" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Enablers section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
         </is>
       </c>
       <c r="H35" s="19" t="inlineStr">

--- a/output/faculty_requests/FBE - end-2026 sustainability reporting request.xlsx
+++ b/output/faculty_requests/FBE - end-2026 sustainability reporting request.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Reporting template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. OPTIONAL highlighted stories" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +41,32 @@
       <b val="1"/>
       <color rgb="00002060"/>
       <sz val="22"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -80,12 +107,6 @@
       <sz val="14"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <color rgb="000E2841"/>
@@ -100,11 +121,9 @@
     <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
+      <color rgb="000563C1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="7">
@@ -116,7 +135,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="000B3040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C1E4F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,17 +155,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C1E4F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -147,12 +166,6 @@
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
     </border>
     <border>
       <left style="thin">
@@ -168,62 +181,73 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -599,7 +623,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col hidden="1" outlineLevel="1" width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" outlineLevel="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" outlineLevel="1" width="24" customWidth="1" min="11" max="11"/>
@@ -650,7 +674,7 @@
 • Provide commentary on progress towards each target (Column M or N)
 • Provide supporting documentation if required (Column O), including links to images
 • Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
-• Your end-2025 responses (where a related target existed) can be viewed by clicking the [+] icon above Columns H–K
+• Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
 • Due: Friday 15 January 2027 (TBC). Questions: Sustainability Strategy team (sustainability-strategy@unimelb.edu.au – TBC)</t>
@@ -728,7 +752,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (for reference – click [+] above to expand)</t>
+          <t>End-2025 reporting (click the ref to see your full SR25 response; [+] above expands a summary)</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -896,7 +920,7 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please provide one or two examples from 2026 of innovative approaches your faculty has used to embed sustainability in teaching and learning (e.g. new or redesigned subjects, curriculum design, pedagogies, assessment approaches or learning resources). Include links to subject pages or resources where available.
 A full list of subjects is not required.</t>
         </is>
@@ -906,9 +930,10 @@
           <t>We will collate examples of innovative sustainability teaching and learning across faculties to inform the Exceptional education section of the 2026 Sustainability Report, and select one or two for short case studies.</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr">
-        <is>
-          <t>4a(ii)</t>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>4a(ii)
+→ view SR25 response</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
@@ -1050,7 +1075,7 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 4b(i) and rated it 'Met or exceeded' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 4b(i) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please nominate up to two alumni from your faculty whose careers or community work demonstrate how they apply sustainability knowledge and skills (name, course and graduating year, a short summary, a link to a profile if available, and whether consent to be featured is likely). If your faculty tracks sustainability-related graduate outcomes in any way, please briefly describe how.</t>
         </is>
       </c>
@@ -1059,9 +1084,10 @@
           <t>We will use nominated alumni to develop short graduate profiles for the 2026 Sustainability Report (subject to consent), and record any faculty approaches to tracking graduate outcomes to inform how this indicator is measured from 2027.</t>
         </is>
       </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>4b(i)</t>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>4b(i)
+→ view SR25 response</t>
         </is>
       </c>
       <c r="I19" s="19" t="inlineStr">
@@ -1109,7 +1135,7 @@
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please provide up to two examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). For each, briefly describe the operational challenge, the researcher's contribution, the University team involved and the result.
 We will collect Campus Living Lab Accelerator Program (CLLAP) projects separately from CI&amp;S – please include other examples only.</t>
         </is>
@@ -1119,9 +1145,10 @@
           <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside CLLAP projects reported by CI&amp;S, and share them with operational teams to identify further collaboration.</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>2a</t>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>2a
+→ view SR25 response</t>
         </is>
       </c>
       <c r="I20" s="19" t="inlineStr">
@@ -1307,7 +1334,7 @@
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please provide one or two examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. For each, briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
 We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from MRE – publication counts are not required.</t>
         </is>
@@ -1317,9 +1344,10 @@
           <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from MRE.</t>
         </is>
       </c>
-      <c r="H24" s="19" t="inlineStr">
-        <is>
-          <t>5b(i)</t>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>5b(i)
+→ view SR25 response</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
@@ -1369,7 +1397,7 @@
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please provide one case study (up to 300 words) of a research project from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. This can be one of the examples from TR2(a), developed in more detail.
 We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.</t>
         </is>
@@ -1379,9 +1407,10 @@
           <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
-      <c r="H25" s="19" t="inlineStr">
-        <is>
-          <t>5b(i)</t>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>5b(i)
+→ view SR25 response</t>
         </is>
       </c>
       <c r="I25" s="19" t="inlineStr">
@@ -1431,7 +1460,7 @@
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please describe how sustainability considerations are built into your faculty's research systems or support – e.g. research planning or approval processes, guidance, graduate researcher induction or training, grant development support. Please highlight any new or improved process introduced in 2026.</t>
         </is>
       </c>
@@ -1440,9 +1469,10 @@
           <t>We will report on how sustainability is being built into research systems and support across the University, and use responses to establish a baseline for this new target.</t>
         </is>
       </c>
-      <c r="H26" s="19" t="inlineStr">
-        <is>
-          <t>5c(ii)</t>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>5c(ii)
+→ view SR25 response</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -1491,7 +1521,7 @@
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please describe up to two examples and any evidence of uptake, resource savings or emissions reductions.</t>
         </is>
       </c>
@@ -1500,9 +1530,10 @@
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H27" s="19" t="inlineStr">
-        <is>
-          <t>5c(ii)</t>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>5c(ii)
+→ view SR25 response</t>
         </is>
       </c>
       <c r="I27" s="19" t="inlineStr">
@@ -1741,7 +1772,7 @@
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 6a and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 6a and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please provide one case study of an activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.</t>
         </is>
       </c>
@@ -1750,9 +1781,10 @@
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H32" s="19" t="inlineStr">
-        <is>
-          <t>6a</t>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>6a
+→ view SR25 response</t>
         </is>
       </c>
       <c r="I32" s="19" t="inlineStr">
@@ -1804,7 +1836,7 @@
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please provide a case study of a living lab which operates within your faculty, including a description of its activities, who is involved (students, researchers, operational staff) and its outputs, outcomes or impact in 2026.
 Please note we will approach living labs funded through the Campus Living Lab Accelerator Program (CLLAP) separately.</t>
         </is>
@@ -1814,9 +1846,10 @@
           <t>We will share examples of living labs from across the University in the 2026 Sustainability Report, alongside CLLAP projects reported by CI&amp;S.</t>
         </is>
       </c>
-      <c r="H33" s="19" t="inlineStr">
-        <is>
-          <t>2a</t>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>2a
+→ view SR25 response</t>
         </is>
       </c>
       <c r="I33" s="19" t="inlineStr">
@@ -1861,7 +1894,7 @@
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) and rated it 'Partially met' (see Column J – click [+] above Columns H–K). Please build on this rather than repeating it, focusing on what is new in 2026.
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and provide a short description of one that has contributed to a Sustainability 2030 outcome.</t>
         </is>
       </c>
@@ -1870,9 +1903,10 @@
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H34" s="19" t="inlineStr">
-        <is>
-          <t>3a(ii)</t>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>3a(ii)
+→ view SR25 response</t>
         </is>
       </c>
       <c r="I34" s="19" t="inlineStr">
@@ -1963,6 +1997,18 @@
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H16" location="'3. SR25 responses'!B12"/>
+    <hyperlink ref="H19" location="'3. SR25 responses'!B13"/>
+    <hyperlink ref="H20" location="'3. SR25 responses'!B8"/>
+    <hyperlink ref="H24" location="'3. SR25 responses'!B14"/>
+    <hyperlink ref="H25" location="'3. SR25 responses'!B14"/>
+    <hyperlink ref="H26" location="'3. SR25 responses'!B15"/>
+    <hyperlink ref="H27" location="'3. SR25 responses'!B15"/>
+    <hyperlink ref="H32" location="'3. SR25 responses'!B16"/>
+    <hyperlink ref="H33" location="'3. SR25 responses'!B8"/>
+    <hyperlink ref="H34" location="'3. SR25 responses'!B10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2013,7 +2059,7 @@
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Friday 4 December 2026 (TBC) (early submission helps us develop case studies).</t>
         </is>
@@ -2021,47 +2067,47 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="22" t="inlineStr"/>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr"/>
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr"/>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr"/>
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr"/>
+      <c r="F9" s="23" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
@@ -2310,4 +2356,482 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>End-2025 target status assessment and reporting (for reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Your SR25 responses – Faculty of Business and Economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>← Back to request</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>FBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>SR25 ref</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>SP2030 target</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>2025 reporting request</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Confirmed end-2025 status</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>OPTION 1: Target-level reporting</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>OPTION 2: Indicator-level reporting</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Supporting information/comments</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Related SR26 indicator(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="160" customHeight="1">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>1a(i)</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>The University is certified carbon neutral by 2025</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Comment on progress to reduce air travel emissions in the faculty</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>While FBE trended down in line with the rest of the Uni, FBE has the second highest emissions per flyer. Despite the research budget being reduced by 20%, FBE has more flyers on average than other Faculties. Unlike the average of the Uni, FBE's emissions increased in Q3 2025 compared with Q3 2024, due to the prevalence of FBE academics attending Northern Hemisphere conferences.</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>There are currently no initiatives to reduce emissions. One Living Lab project was investigated but was not possibly due to non-cooperation by the Uni's travel partner</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>https://app.powerbi.com/links/SI8xYFLga4?ctid=0e5bf3cf-1ff4-46b7-9176-52c538c22a4d&amp;pbi_source=linkShare&amp;bookmarkGuid=499326eb-68f1-43e0-a3e6-0f252ee44ccb</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr"/>
+    </row>
+    <row r="8" ht="160" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>2a</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>The University has curated living labs covering the priority areas of this Plan</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Please provide a case study of a living lab which operates within the faculty/portfolio, including a description of its activities and impact. 
+Please note we will approach living labs funded through the Campus Living Lab Accelerator program (CLLAP) separately report on their activities.</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>CLLAP report on University Investor Stewardship provided separately</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>TR1(a), EN1(b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="160" customHeight="1">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>3a(i)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Please update data on sustainability-focused staff in the faculty/portfolio provided in the previous reporting period (additional staff/those who have left the University) (see Columns G [2024] and J [mid-2025])</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>This is done in multiple ways. Faculty leadership will be increasingly guided by the formation of the Sustainability Steering Committee under the leadership of AD Sust A/Prof Ben Neville, including Dr David Keith, Prof Brad Potter, Prof Rosemary Addis, Prof Allan Tate, Prof Daiane Scaraboto, A/Prof Leslie Martin, Dr Gabriele Lattanzio. This Committee has also formed a dedicated Sustainability Teaching Working Group (see case study).  
+In teaching within Departments, focus remains on increasing the prevalance of sustainability content including assessments across subjects. Staff collaborate across department boundaries in the development of teaching cases and the recent collbaoration with accounting staff and Dilun Duwa, focusing on an indigenous business, is a good example.   Multiple examples of sustainability-related research projects involving staff from multiple academic departments</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="19" t="inlineStr"/>
+    </row>
+    <row r="10" ht="160" customHeight="1">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>3a(ii)</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Please list sustainability-focused knowledge sharing activities or communities of practice active in the faculty/portfolio in 2025, and provide a short case study of one of these.</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>The Faculty leads many cross department events and workshops to further sustainability knowledge and integration. For example, FBE faciliating the Shared Value Project exec ed for the 3rd time in 2025 as well as the SVP summit in 2025 at Melbourne Connect. FBE is deepening its relationship with SVP - which will provide a key highly visable and impactful  pathway to embedding sustsinability and shared value into teaching as well  offering myriad research opportunities. 
+The Faculty led a University research engagement event - the Sustainable Finance Futures Forum - on September 17 within Sustainability Week. The event was attended by approximately 80 people from industry and the University community. It featured a keynote by Director of the University's Sustainable Finance Hub, Simon O'Connor, followed by an industry panel and then workshop session on climate scenario analyses led by A/Prof Ben Neville</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="19" t="inlineStr"/>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>EN1(c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="160" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>3d(ii)</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>Academic and professional staff have increased their participation in and contribution to formal and non_x0002_formal learning to develop their general and role-specific sustainability skills</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Have any staff participated in sustainability-focused professional development in 2025? If yes, what kinds of activities have staff participated in and how are these learnings being applied in the faculty/portfolio?
+Please note, there is no need to include data on participation in Green Impact ('Green teams'), as this is reported on centrally.</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>There have been no dedicated workshops to upskill staff in relation to SP2030 targets, although there have been multiple other sustainability-themed workshops and events led by the Faculty (see above)</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="19" t="inlineStr"/>
+      <c r="I11" s="19" t="inlineStr"/>
+    </row>
+    <row r="12" ht="160" customHeight="1">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>4a(ii)</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Please describe any efforts within your faculty to embed sustainability in the curriculum in line with this target.</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>The refresh of the Bachelor of Commerce BCOM refresh included explicitly embedding sustainability in course level learning outcomes, major level learning outcomes, and is now a specialisation (Ethics and Sustainability) available to students across all majors. 
+See also Sust teaching case study p2</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr"/>
+      <c r="H12" s="19" t="inlineStr"/>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>EE1(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="160" customHeight="1">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>4b(i)</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Graduates have increased capabilities to shape, lead 
+and succeed in the careers, communities and industries 
+of sustainable societies (year on year).</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Is there any way to measure graduate outcomes related to sustainability in your faculty? If so, please describe.</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>A new 'specialisation' (similar to a Major) in Ethics and Sustainability has been approved for the Bachelor of Commerce and available in 2026. The previous Discovery subject Sustainable Commerce has been discontinued.
+In Work-Integrated-Learning subjects, such as WorkHUB, Business Practicum and Management Consulting, have pivoted to ensure sustainability related projects are offered in all semesters.  Case comps, and other co-curricular activities explicitly focus on sustainability related themes.
+aSSERT, a sustainability competency self-assessment co-developed with FEIT and SCI faculty, was piloted in third year undergraduate sustainability elective subject (MGMT30008), students reportedly were able to develop competencies related to "embracing complexity" and "envisioning sustainable futures"  
+See also Sust teaching case study p2</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr"/>
+      <c r="H13" s="19" t="inlineStr"/>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>EE1(d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="160" customHeight="1">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>5b(i)</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>The highest quality research is conducted that contributes to knowledge, action, and impact across the disciplinary and interdisciplinary dimensions of sustainability.</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Please update data on sustainability-, climate- or environment-focused research institutes, and provide a case study of their key research impacts in 2025.</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>Several departments have completed high quality sustainability-focused research, which includes papers published in peer reviwed research journals and a range of commissioned research for diverse industry partners including the national accounting standard setting body, which focus on a range of sustainability-related topics.</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>See M&amp;M Sust Research Hub case study p2</t>
+        </is>
+      </c>
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>https://fbe.unimelb.edu.au/research/our-research-at-a-glance</t>
+        </is>
+      </c>
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>TR2(a), TR2(d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="160" customHeight="1">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>5c(ii)</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Researchers make considered decisions on the sustainability impact of their research practices and activities</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Are there any efforts within the faculty to make research practices more sustainable? If so, please describe these activities</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr"/>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>The Department of Management &amp; Marketing Sustainable Research Hub is leading on 'Graduate Researcher Training for Sustainability-Related Research'. Equipping the next generation of researchers with the interdisciplinary and transdisciplinary knowledge and skills, and systems thinking competencies that enables them to recognize and pursue complex sustainability problems in their research, and to recognize the potential impact of their research on sustainability concerns. Development of these capabilities includes curriculum design, experiential learning opportunities, research ethics protocols, and institutional support needed to foster impactful sustainability research. (Also see case study p2)</t>
+        </is>
+      </c>
+      <c r="H15" s="19" t="inlineStr">
+        <is>
+          <t>https://fbe.unimelb.edu.au/managementmarketing/research/the-sustainability-hub</t>
+        </is>
+      </c>
+      <c r="I15" s="19" t="inlineStr">
+        <is>
+          <t>TR3(a), TR3(b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="160" customHeight="1">
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>6a</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>The University has an increased understanding of sustainability from an Indigenous perspective through co-created or Indigenous-led reciprocal learning</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Please provide a case study on activities in the faculty (related to education, research or partnerships) which operate at the nexus between Indigenous knowledges and the western concept of 'sustainability'.</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>The Dilin Duwa Centre for Indigenous Business Leadership is developing research, teaching and engagement programs to enhance the economic skill base of Indigenous Australians, including through entrepreneurship, jobs and procurement. 
+The Mabo Centre works to support Traditional Owners achieve successful Native Title outcomes for their communities through research, training, excahange and acceleration.
+PhD student Caleb Adams' cross disciplinary thesis topic is 'Understanding and Unlocking Financial Capital: Empowering First Nations Leadership in and for a Green Economy'</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr"/>
+      <c r="H16" s="19" t="inlineStr">
+        <is>
+          <t>https://dilinduwa.com.au/
+https://mabocentre.com/</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>EN1(a)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:I3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/faculty_requests/FBE - end-2026 sustainability reporting request.xlsx
+++ b/output/faculty_requests/FBE - end-2026 sustainability reporting request.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Reporting template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. OPTIONAL highlighted stories" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2153,217 +2153,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>End 2026 target status</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Data owner confirms</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Request status</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Please select from dropdown</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Not sent</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Partially – see comments</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Chased</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Support meeting</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Under review</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Not required</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2834,4 +2623,215 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>End 2026 target status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Data owner confirms</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Request status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Y/N</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Target status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Response count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Please select from dropdown</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Partially – see comments</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Chased</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Support meeting</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Not required</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>